--- a/v0.4.4-埋点表清单.xlsx
+++ b/v0.4.4-埋点表清单.xlsx
@@ -12,8 +12,9 @@
     <sheet name="B-钓位与鱼塘" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="C-状态机" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="D-咬钩与产出" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="E-系统性能" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="慢测验证" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="D-成长与进度" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="E-系统性能" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="慢测验证" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -434,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I34"/>
+  <dimension ref="A1:I39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1166,140 +1167,146 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
+          <t>B钓位鱼塘</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>pond_ecology_catchup</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>日志</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>空鱼塘唤醒时事务化补算生态</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>pondId
+offlineMs
+replaySteps
+migrated
+supplemented
+durationMs
+catchupCompacted</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>{"catchupCompacted":false,"replaySteps":2}</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>pondEcology.ts</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
           <t>C状态机</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>fishing_phase_transition</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
         <is>
           <t>metrics+日志</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>phase 变更；D-L2-16 metrics 仅短码 f/t/c；ADMIN-OBS-1.3 默认 bot 不落库（METRICS_BOT_PHASE=1 恢复）；日志仍用全称</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>f
 t
 c</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>{"f":4,"t":5,"c":"bite_hook"}</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>已实现</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>fishingObservability.ts</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>C状态机</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>phase_transition_invalid</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>日志+metrics</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>非法跳转；metrics 短码 f/t/c；日志可读全称</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>f
 t
 c</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>{"f":0,"t":5,"c":"bite_hook"}</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>已实现</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>fishingStateMachine.ts</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>D咬钩产出</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>bite_tick_miss</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>metrics</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>waiting 未咬钩（D-L2-15 默认不落库；METRICS_BITE_TICK_PERSIST=1）</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>pondId</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>已废弃默认</t>
+          <t>已实现</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1316,138 +1323,138 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
+          <t>bite_tick_miss</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>metrics</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>waiting 未咬钩（D-L2-15 默认不落库；METRICS_BITE_TICK_PERSIST=1）</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>pondId</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>已废弃默认</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>fishingStateMachine.ts</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>D咬钩产出</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
           <t>bite_tick_hit</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
         <is>
           <t>metrics</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>waiting 咬钩（D-L2-15 默认不落库，并入 bite_hook）</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>speciesId
 quality</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>已废弃默认</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>fishingStateMachine.ts</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>D咬钩产出</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>bite_hook</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
         <is>
           <t>metrics</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>上钩+会话累计（sessionHooks/Escapes/MissTicks）</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>sessionHooks
 sessionMissTicks</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>已实现</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
         <is>
           <t>fishingStateMachine.ts</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>D咬钩产出</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>pending_catch_created</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>metrics</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>待领取创建</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>fishId</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>已实现</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>inventory.ts</t>
         </is>
       </c>
     </row>
@@ -1459,7 +1466,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>pending_catch_accept</t>
+          <t>pending_catch_created</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -1469,7 +1476,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>领取成功</t>
+          <t>待领取创建</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1489,12 +1496,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>已实现(别名catch_accept)</t>
+          <t>已实现</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>socketPondHandlers.ts</t>
+          <t>inventory.ts</t>
         </is>
       </c>
     </row>
@@ -1506,7 +1513,7 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>pending_catch_expired</t>
+          <t>pending_catch_accept</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -1516,7 +1523,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>待领取超时</t>
+          <t>领取成功</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -1536,12 +1543,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>已实现</t>
+          <t>已实现(别名catch_accept)</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>inventory.ts</t>
+          <t>socketPondHandlers.ts</t>
         </is>
       </c>
     </row>
@@ -1553,7 +1560,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>bait_depleted</t>
+          <t>pending_catch_expired</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -1563,12 +1570,12 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>饵耗尽</t>
+          <t>待领取超时</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>baitId</t>
+          <t>fishId</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1588,7 +1595,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>fishingStateMachine.ts</t>
+          <t>inventory.ts</t>
         </is>
       </c>
     </row>
@@ -1600,80 +1607,80 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
+          <t>bait_depleted</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>metrics</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>饵耗尽</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>baitId</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>fishingStateMachine.ts</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>D咬钩产出</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
           <t>escape</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
         <is>
           <t>metrics</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>脱钩+会话累计</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>sessionEscapes
 sessionHooks</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>P0</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>已实现</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>fishingStateMachine.ts</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>D咬钩产出</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>fishing_start</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>metrics</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>开始钓鱼</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>pondId</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>P1</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -1695,7 +1702,7 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>fishing_stop</t>
+          <t>fishing_start</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -1705,7 +1712,7 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>停止钓鱼</t>
+          <t>开始钓鱼</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -1742,7 +1749,7 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>abandon_fishing</t>
+          <t>fishing_stop</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -1752,7 +1759,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>&lt;30s 停止</t>
+          <t>停止钓鱼</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1777,34 +1784,34 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>fishingMetrics.ts</t>
+          <t>fishingStateMachine.ts</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>E性能</t>
+          <t>D咬钩产出</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>tick_fishing_phases_duration_ms</t>
+          <t>abandon_fishing</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>聚合日志</t>
+          <t>metrics</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>200ms tick 耗时</t>
+          <t>&lt;30s 停止</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>durationMs</t>
+          <t>pondId</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -1814,7 +1821,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -1824,44 +1831,46 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>serverLoops.ts</t>
+          <t>fishingMetrics.ts</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>E性能</t>
+          <t>D成长进度</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>bite_check_loop_duration_ms</t>
+          <t>admission_fee_charged</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>聚合日志</t>
+          <t>metrics</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>咬钩循环耗时</t>
+          <t>收费塘满2h扣费成功</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>durationMs</t>
+          <t>playerId
+pondId
+feePer2h</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"feePer2h":200,"chargeIndex":1}</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -1871,199 +1880,436 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>serverLoops.ts</t>
+          <t>playerProgress.ts</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
+          <t>D成长进度</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>fishing_stopped_insufficient_gold</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>metrics</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>金币不足停钓</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>playerId
+pondId</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>{"feePer2h":200}</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>playerProgress.ts</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>D成长进度</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>onboarding_completed</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>metrics</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>新手引导完成</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>playerId</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>{"pondId":"pond-novice"}</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>playerProgress.ts</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>D成长进度</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>pond_proficiency_capped</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>metrics</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>塘熟练度满/锁满停发塘XP</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>playerId
+pondId</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>{"source":"catch"}</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>playerProgress.ts</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
           <t>E性能</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>tick_fishing_phases_duration_ms</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>聚合日志</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>200ms tick 耗时</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>durationMs</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>serverLoops.ts</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>E性能</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>bite_check_loop_duration_ms</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>聚合日志</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>咬钩循环耗时</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>durationMs</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>serverLoops.ts</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>E性能</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>snapshot_build_duration_ms</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
+      <c r="C36" s="2" t="inlineStr">
         <is>
           <t>聚合日志</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>buildSnapshot 耗时</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E36" s="2" t="inlineStr">
         <is>
           <t>durationMs
 pondId</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>已实现</t>
-        </is>
-      </c>
-      <c r="I31" s="2" t="inlineStr">
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
         <is>
           <t>gameState.ts</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>E性能</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="B37" s="2" t="inlineStr">
         <is>
           <t>socket_broadcast_fanout</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
+      <c r="C37" s="2" t="inlineStr">
         <is>
           <t>指标+可选日志</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="D37" s="2" t="inlineStr">
         <is>
           <t>广播 fanout；默认 Prometheus counter，FANOUT_LOG_INFO=1 才打 info</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr">
         <is>
           <t>fanoutCount
 channel
 pondId</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>已实现</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="inlineStr">
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
         <is>
           <t>serverLoops.ts</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>E性能</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>sqlite_query_slow</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr">
+      <c r="C38" s="2" t="inlineStr">
         <is>
           <t>日志</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>慢 SQL</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="E38" s="2" t="inlineStr">
         <is>
           <t>label
 durationMs
 rows</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>已实现</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr">
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
         <is>
           <t>db.ts</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>E性能</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
         <is>
           <t>admin_route_duration_ms</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr">
+      <c r="C39" s="2" t="inlineStr">
         <is>
           <t>日志</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="D39" s="2" t="inlineStr">
         <is>
           <t>Admin 接口耗时</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="E39" s="2" t="inlineStr">
         <is>
           <t>route
 durationMs</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>已实现</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr">
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
         <is>
           <t>admin.ts</t>
         </is>
@@ -2584,7 +2830,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2878,6 +3124,59 @@
       <c r="I6" s="2" t="inlineStr">
         <is>
           <t>gameState.ts</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>B钓位鱼塘</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>pond_ecology_catchup</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>日志</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>空鱼塘唤醒时事务化补算生态</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>pondId
+offlineMs
+replaySteps
+migrated
+supplemented
+durationMs
+catchupCompacted</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>{"catchupCompacted":false,"replaySteps":2}</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>pondEcology.ts</t>
         </is>
       </c>
     </row>
@@ -3654,6 +3953,270 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:I5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="28" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>类别</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>事件名</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>类型</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>触发时机</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>必填字段(核心)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>示例payload</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>优先级</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>状态</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>推荐落点文件</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>D成长进度</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>admission_fee_charged</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>metrics</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>收费塘满2h扣费成功</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>playerId
+pondId
+feePer2h</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>{"feePer2h":200,"chargeIndex":1}</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>playerProgress.ts</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>D成长进度</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>fishing_stopped_insufficient_gold</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>metrics</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>金币不足停钓</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>playerId
+pondId</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>{"feePer2h":200}</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>playerProgress.ts</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>D成长进度</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>onboarding_completed</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>metrics</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>新手引导完成</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>playerId</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>{"pondId":"pond-novice"}</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>playerProgress.ts</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>D成长进度</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>pond_proficiency_capped</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>metrics</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>塘熟练度满/锁满停发塘XP</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>playerId
+pondId</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>{"source":"catch"}</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>playerProgress.ts</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -4008,7 +4571,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/v0.4.4-埋点表清单.xlsx
+++ b/v0.4.4-埋点表清单.xlsx
@@ -13,8 +13,10 @@
     <sheet name="C-状态机" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="D-咬钩与产出" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="D-成长与进度" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="E-系统性能" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="慢测验证" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="D-装备" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="D-风险事件" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="E-系统性能" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="慢测验证" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -435,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I39"/>
+  <dimension ref="A1:I45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2030,37 +2032,39 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>E性能</t>
+          <t>D装备</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>tick_fishing_phases_duration_ms</t>
+          <t>bait_use</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>聚合日志</t>
+          <t>metrics</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>200ms tick 耗时</t>
+          <t>咬钩使用进阶饵扣金</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>durationMs</t>
+          <t>playerId
+baitId
+cost</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"baitId":"bait-veg","cost":15}</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -2070,44 +2074,45 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>serverLoops.ts</t>
+          <t>gear.ts</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>E性能</t>
+          <t>D装备</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>bite_check_loop_duration_ms</t>
+          <t>rod_buy</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>聚合日志</t>
+          <t>metrics</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>咬钩循环耗时</t>
+          <t>购买钓竿</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>durationMs</t>
+          <t>playerId
+rodId</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"rodId":"rod-tai","cost":2500}</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -2117,201 +2122,589 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>serverLoops.ts</t>
+          <t>shop.ts</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
+          <t>D装备</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>rod_broke</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>metrics</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>超规格满N次销毁钓竿</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>playerId
+rodId</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>{"sizeM":0.5,"oversizeLandings":3}</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>gear.ts</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>D装备</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>vessel_buy</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>metrics</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>购买船具（不可使用）</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>playerId
+vesselId</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>{"vesselId":"vessel-raft","cost":15000}</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>shop.ts</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>D风险</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>forbidden_pond_fine</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>metrics</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>禁止塘巡警超时罚款+当日禁钓</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>playerId
+pondId</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>{"charged":800,"coinsAfter":0}</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>forbiddenPolice.ts</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>D风险</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>forbidden_pond_escaped</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>metrics</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>禁止塘巡警时限内离塘免罚，2h禁入</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>playerId
+pondId</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>{"untilMs":0}</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>forbiddenPolice.ts</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
           <t>E性能</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>tick_fishing_phases_duration_ms</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>聚合日志</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>200ms tick 耗时</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>durationMs</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>serverLoops.ts</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>E性能</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>bite_check_loop_duration_ms</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>聚合日志</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>咬钩循环耗时</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>durationMs</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>serverLoops.ts</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>E性能</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t>snapshot_build_duration_ms</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr">
+      <c r="C42" s="2" t="inlineStr">
         <is>
           <t>聚合日志</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="D42" s="2" t="inlineStr">
         <is>
           <t>buildSnapshot 耗时</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="E42" s="2" t="inlineStr">
         <is>
           <t>durationMs
 pondId</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="F42" s="2" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr">
+      <c r="G42" s="2" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>已实现</t>
-        </is>
-      </c>
-      <c r="I36" s="2" t="inlineStr">
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
         <is>
           <t>gameState.ts</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
         <is>
           <t>E性能</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
+      <c r="B43" s="2" t="inlineStr">
         <is>
           <t>socket_broadcast_fanout</t>
         </is>
       </c>
-      <c r="C37" s="2" t="inlineStr">
+      <c r="C43" s="2" t="inlineStr">
         <is>
           <t>指标+可选日志</t>
         </is>
       </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="D43" s="2" t="inlineStr">
         <is>
           <t>广播 fanout；默认 Prometheus counter，FANOUT_LOG_INFO=1 才打 info</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="E43" s="2" t="inlineStr">
         <is>
           <t>fanoutCount
 channel
 pondId</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
+      <c r="F43" s="2" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr">
+      <c r="G43" s="2" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>已实现</t>
-        </is>
-      </c>
-      <c r="I37" s="2" t="inlineStr">
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
         <is>
           <t>serverLoops.ts</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>E性能</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
         <is>
           <t>sqlite_query_slow</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr">
+      <c r="C44" s="2" t="inlineStr">
         <is>
           <t>日志</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>慢 SQL</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t>label
 durationMs
 rows</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="F44" s="2" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr">
+      <c r="G44" s="2" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>已实现</t>
-        </is>
-      </c>
-      <c r="I38" s="2" t="inlineStr">
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
         <is>
           <t>db.ts</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t>E性能</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
+      <c r="B45" s="2" t="inlineStr">
         <is>
           <t>admin_route_duration_ms</t>
         </is>
       </c>
-      <c r="C39" s="2" t="inlineStr">
+      <c r="C45" s="2" t="inlineStr">
         <is>
           <t>日志</t>
         </is>
       </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="D45" s="2" t="inlineStr">
         <is>
           <t>Admin 接口耗时</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="E45" s="2" t="inlineStr">
         <is>
           <t>route
 durationMs</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
+      <c r="F45" s="2" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
-      <c r="G39" s="2" t="inlineStr">
+      <c r="G45" s="2" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="H39" s="2" t="inlineStr">
-        <is>
-          <t>已实现</t>
-        </is>
-      </c>
-      <c r="I39" s="2" t="inlineStr">
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
         <is>
           <t>admin.ts</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>用例</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>脚本</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>状态</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>说明</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>server observability</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>npm run verify:server-observability</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>join/phase/timeline</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>pending timeout</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>npx tsx scripts/verify-pending-timeout.ts</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>可选</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>慢测 pending_catch_expired</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>afk diag</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>npx tsx scripts/verify-afk-diag.ts</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>断线宽限</t>
         </is>
       </c>
     </row>
@@ -4217,6 +4610,439 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:I5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="28" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>类别</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>事件名</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>类型</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>触发时机</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>必填字段(核心)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>示例payload</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>优先级</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>状态</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>推荐落点文件</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>D装备</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>bait_use</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>metrics</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>咬钩使用进阶饵扣金</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>playerId
+baitId
+cost</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>{"baitId":"bait-veg","cost":15}</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>gear.ts</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>D装备</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>rod_buy</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>metrics</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>购买钓竿</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>playerId
+rodId</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>{"rodId":"rod-tai","cost":2500}</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>shop.ts</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>D装备</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>rod_broke</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>metrics</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>超规格满N次销毁钓竿</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>playerId
+rodId</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>{"sizeM":0.5,"oversizeLandings":3}</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>gear.ts</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>D装备</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>vessel_buy</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>metrics</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>购买船具（不可使用）</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>playerId
+vesselId</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>{"vesselId":"vessel-raft","cost":15000}</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>shop.ts</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="28" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>类别</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>事件名</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>类型</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>触发时机</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>必填字段(核心)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>示例payload</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>优先级</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>状态</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>推荐落点文件</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>D风险</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>forbidden_pond_fine</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>metrics</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>禁止塘巡警超时罚款+当日禁钓</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>playerId
+pondId</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>{"charged":800,"coinsAfter":0}</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>forbiddenPolice.ts</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>D风险</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>forbidden_pond_escaped</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>metrics</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>禁止塘巡警时限内离塘免罚，2h禁入</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>playerId
+pondId</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>{"untilMs":0}</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>forbiddenPolice.ts</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -4569,106 +5395,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>用例</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>脚本</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>状态</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>说明</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>server observability</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>npm run verify:server-observability</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>已实现</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>join/phase/timeline</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>pending timeout</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>npx tsx scripts/verify-pending-timeout.ts</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>可选</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>慢测 pending_catch_expired</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>afk diag</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>npx tsx scripts/verify-afk-diag.ts</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>已实现</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>断线宽限</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/v0.4.4-埋点表清单.xlsx
+++ b/v0.4.4-埋点表清单.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I45"/>
+  <dimension ref="A1:I46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2321,37 +2321,38 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>E性能</t>
+          <t>D成长进度</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>tick_fishing_phases_duration_ms</t>
+          <t>gameplay_debug_action</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>聚合日志</t>
+          <t>metrics</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>200ms tick 耗时</t>
+          <t>玩法 Debug 菜单操作</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>durationMs</t>
+          <t>playerId
+action</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"action":"level_up","ok":true}</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -2361,7 +2362,7 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>serverLoops.ts</t>
+          <t>gameplayDebug.ts</t>
         </is>
       </c>
     </row>
@@ -2373,7 +2374,7 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>bite_check_loop_duration_ms</t>
+          <t>tick_fishing_phases_duration_ms</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -2383,7 +2384,7 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>咬钩循环耗时</t>
+          <t>200ms tick 耗时</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -2420,187 +2421,234 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
+          <t>bite_check_loop_duration_ms</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>聚合日志</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>咬钩循环耗时</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>durationMs</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>serverLoops.ts</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>E性能</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
           <t>snapshot_build_duration_ms</t>
         </is>
       </c>
-      <c r="C42" s="2" t="inlineStr">
+      <c r="C43" s="2" t="inlineStr">
         <is>
           <t>聚合日志</t>
         </is>
       </c>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="D43" s="2" t="inlineStr">
         <is>
           <t>buildSnapshot 耗时</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="E43" s="2" t="inlineStr">
         <is>
           <t>durationMs
 pondId</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="F43" s="2" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr">
+      <c r="G43" s="2" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>已实现</t>
-        </is>
-      </c>
-      <c r="I42" s="2" t="inlineStr">
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
         <is>
           <t>gameState.ts</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>E性能</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
         <is>
           <t>socket_broadcast_fanout</t>
         </is>
       </c>
-      <c r="C43" s="2" t="inlineStr">
+      <c r="C44" s="2" t="inlineStr">
         <is>
           <t>指标+可选日志</t>
         </is>
       </c>
-      <c r="D43" s="2" t="inlineStr">
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>广播 fanout；默认 Prometheus counter，FANOUT_LOG_INFO=1 才打 info</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t>fanoutCount
 channel
 pondId</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
+      <c r="F44" s="2" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
-      <c r="G43" s="2" t="inlineStr">
+      <c r="G44" s="2" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t>已实现</t>
-        </is>
-      </c>
-      <c r="I43" s="2" t="inlineStr">
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
         <is>
           <t>serverLoops.ts</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t>E性能</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
+      <c r="B45" s="2" t="inlineStr">
         <is>
           <t>sqlite_query_slow</t>
         </is>
       </c>
-      <c r="C44" s="2" t="inlineStr">
+      <c r="C45" s="2" t="inlineStr">
         <is>
           <t>日志</t>
         </is>
       </c>
-      <c r="D44" s="2" t="inlineStr">
+      <c r="D45" s="2" t="inlineStr">
         <is>
           <t>慢 SQL</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="E45" s="2" t="inlineStr">
         <is>
           <t>label
 durationMs
 rows</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="F45" s="2" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr">
+      <c r="G45" s="2" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>已实现</t>
-        </is>
-      </c>
-      <c r="I44" s="2" t="inlineStr">
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
         <is>
           <t>db.ts</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t>E性能</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
         <is>
           <t>admin_route_duration_ms</t>
         </is>
       </c>
-      <c r="C45" s="2" t="inlineStr">
+      <c r="C46" s="2" t="inlineStr">
         <is>
           <t>日志</t>
         </is>
       </c>
-      <c r="D45" s="2" t="inlineStr">
+      <c r="D46" s="2" t="inlineStr">
         <is>
           <t>Admin 接口耗时</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="E46" s="2" t="inlineStr">
         <is>
           <t>route
 durationMs</t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr">
+      <c r="F46" s="2" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
-      <c r="G45" s="2" t="inlineStr">
+      <c r="G46" s="2" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="H45" s="2" t="inlineStr">
-        <is>
-          <t>已实现</t>
-        </is>
-      </c>
-      <c r="I45" s="2" t="inlineStr">
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
         <is>
           <t>admin.ts</t>
         </is>
@@ -4346,7 +4394,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4596,6 +4644,54 @@
       <c r="I5" s="2" t="inlineStr">
         <is>
           <t>playerProgress.ts</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>D成长进度</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>gameplay_debug_action</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>metrics</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>玩法 Debug 菜单操作</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>playerId
+action</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>{"action":"level_up","ok":true}</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>gameplayDebug.ts</t>
         </is>
       </c>
     </row>

--- a/v0.4.4-埋点表清单.xlsx
+++ b/v0.4.4-埋点表清单.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I46"/>
+  <dimension ref="A1:I47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2369,37 +2369,38 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>E性能</t>
+          <t>D成长进度</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>tick_fishing_phases_duration_ms</t>
+          <t>fish_returned_to_pond</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>聚合日志</t>
+          <t>metrics</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>200ms tick 耗时</t>
+          <t>回鱼入塘增重并发奖</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>durationMs</t>
+          <t>playerId
+pondId</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"speciesId":"crucian","sizeM":0.2,"gold":56,"sizeGainM":0.03}</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -2409,7 +2410,7 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>serverLoops.ts</t>
+          <t>returnFish.ts</t>
         </is>
       </c>
     </row>
@@ -2421,7 +2422,7 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>bite_check_loop_duration_ms</t>
+          <t>tick_fishing_phases_duration_ms</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -2431,7 +2432,7 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>咬钩循环耗时</t>
+          <t>200ms tick 耗时</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -2468,187 +2469,234 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
+          <t>bite_check_loop_duration_ms</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>聚合日志</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>咬钩循环耗时</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>durationMs</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>serverLoops.ts</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>E性能</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
           <t>snapshot_build_duration_ms</t>
         </is>
       </c>
-      <c r="C43" s="2" t="inlineStr">
+      <c r="C44" s="2" t="inlineStr">
         <is>
           <t>聚合日志</t>
         </is>
       </c>
-      <c r="D43" s="2" t="inlineStr">
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>buildSnapshot 耗时</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t>durationMs
 pondId</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
+      <c r="F44" s="2" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
-      <c r="G43" s="2" t="inlineStr">
+      <c r="G44" s="2" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t>已实现</t>
-        </is>
-      </c>
-      <c r="I43" s="2" t="inlineStr">
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
         <is>
           <t>gameState.ts</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t>E性能</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
+      <c r="B45" s="2" t="inlineStr">
         <is>
           <t>socket_broadcast_fanout</t>
         </is>
       </c>
-      <c r="C44" s="2" t="inlineStr">
+      <c r="C45" s="2" t="inlineStr">
         <is>
           <t>指标+可选日志</t>
         </is>
       </c>
-      <c r="D44" s="2" t="inlineStr">
+      <c r="D45" s="2" t="inlineStr">
         <is>
           <t>广播 fanout；默认 Prometheus counter，FANOUT_LOG_INFO=1 才打 info</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="E45" s="2" t="inlineStr">
         <is>
           <t>fanoutCount
 channel
 pondId</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="F45" s="2" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr">
+      <c r="G45" s="2" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>已实现</t>
-        </is>
-      </c>
-      <c r="I44" s="2" t="inlineStr">
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
         <is>
           <t>serverLoops.ts</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t>E性能</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
         <is>
           <t>sqlite_query_slow</t>
         </is>
       </c>
-      <c r="C45" s="2" t="inlineStr">
+      <c r="C46" s="2" t="inlineStr">
         <is>
           <t>日志</t>
         </is>
       </c>
-      <c r="D45" s="2" t="inlineStr">
+      <c r="D46" s="2" t="inlineStr">
         <is>
           <t>慢 SQL</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="E46" s="2" t="inlineStr">
         <is>
           <t>label
 durationMs
 rows</t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr">
+      <c r="F46" s="2" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
-      <c r="G45" s="2" t="inlineStr">
+      <c r="G46" s="2" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="H45" s="2" t="inlineStr">
-        <is>
-          <t>已实现</t>
-        </is>
-      </c>
-      <c r="I45" s="2" t="inlineStr">
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
         <is>
           <t>db.ts</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
         <is>
           <t>E性能</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
+      <c r="B47" s="2" t="inlineStr">
         <is>
           <t>admin_route_duration_ms</t>
         </is>
       </c>
-      <c r="C46" s="2" t="inlineStr">
+      <c r="C47" s="2" t="inlineStr">
         <is>
           <t>日志</t>
         </is>
       </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="D47" s="2" t="inlineStr">
         <is>
           <t>Admin 接口耗时</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="E47" s="2" t="inlineStr">
         <is>
           <t>route
 durationMs</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
+      <c r="F47" s="2" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr">
+      <c r="G47" s="2" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="H46" s="2" t="inlineStr">
-        <is>
-          <t>已实现</t>
-        </is>
-      </c>
-      <c r="I46" s="2" t="inlineStr">
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
         <is>
           <t>admin.ts</t>
         </is>
@@ -4394,7 +4442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4692,6 +4740,54 @@
       <c r="I6" s="2" t="inlineStr">
         <is>
           <t>gameplayDebug.ts</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>D成长进度</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>fish_returned_to_pond</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>metrics</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>回鱼入塘增重并发奖</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>playerId
+pondId</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>{"speciesId":"crucian","sizeM":0.2,"gold":56,"sizeGainM":0.03}</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>returnFish.ts</t>
         </is>
       </c>
     </row>

--- a/v0.4.4-埋点表清单.xlsx
+++ b/v0.4.4-埋点表清单.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I47"/>
+  <dimension ref="A1:I55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2395,7 +2395,7 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>{"speciesId":"crucian","sizeM":0.2,"gold":56,"sizeGainM":0.03}</t>
+          <t>{"speciesId":"crucian","sizeM":0.2,"gold":56,"sizeGainM":0.03,"auto":false}</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -2417,37 +2417,38 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>E性能</t>
+          <t>D成长进度</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>tick_fishing_phases_duration_ms</t>
+          <t>return_fee_mode_selected</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>聚合日志</t>
+          <t>metrics</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>200ms tick 耗时</t>
+          <t>进塘双价模式选择</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>durationMs</t>
+          <t>playerId
+pondId</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"mode":"auto_return","feePer2h":350}</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -2457,44 +2458,45 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>serverLoops.ts</t>
+          <t>socketPondHandlers.ts</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>E性能</t>
+          <t>D成长进度</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>bite_check_loop_duration_ms</t>
+          <t>fish_auto_returned</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>聚合日志</t>
+          <t>metrics</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>咬钩循环耗时</t>
+          <t>达标鱼自动回塘</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>durationMs</t>
+          <t>playerId
+pondId</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"speciesId":"crucian","sizeM":0.28,"gold":120,"auto":true}</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -2504,199 +2506,582 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>serverLoops.ts</t>
+          <t>returnFish.ts</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
+          <t>D装备</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>groundbait_cast_started</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>metrics</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>开始打窝扣金</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>playerId
+groundbaitId</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>{"costGold":30,"stackBefore":0}</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>groundbait.ts</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>D装备</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>groundbait_applied</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>metrics</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>打窝完成叠层</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>playerId
+pondId</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>{"stackAfter":1,"biteBonus":0.006}</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>groundbait.ts</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>D装备</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>groundbait_rejected</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>metrics</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>打窝拒绝</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>playerId
+reason</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>{"reason":"gold","code":"INSUFFICIENT_GOLD"}</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>groundbait.ts</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>D成长进度</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>achievement_unlocked</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>metrics</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>成就解锁</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>playerId
+achievementId</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>{"achievementId":"ach-first-catch"}</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>achievements.ts</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>D成长进度</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>album_pin_changed</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>metrics</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>相册钉选变更</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>playerId
+pinCount
+action</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>{"pinCount":3,"action":"pin"}</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>album.ts</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>D成长进度</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>profile_hub_opened</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>metrics</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>打开个人中心</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>playerId
+tab</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>{"tab":"album"}</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>profileHub.ts</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
           <t>E性能</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>tick_fishing_phases_duration_ms</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>聚合日志</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>200ms tick 耗时</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>durationMs</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>serverLoops.ts</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>E性能</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>bite_check_loop_duration_ms</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>聚合日志</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>咬钩循环耗时</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>durationMs</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>serverLoops.ts</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>E性能</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
         <is>
           <t>snapshot_build_duration_ms</t>
         </is>
       </c>
-      <c r="C44" s="2" t="inlineStr">
+      <c r="C52" s="2" t="inlineStr">
         <is>
           <t>聚合日志</t>
         </is>
       </c>
-      <c r="D44" s="2" t="inlineStr">
+      <c r="D52" s="2" t="inlineStr">
         <is>
           <t>buildSnapshot 耗时</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="E52" s="2" t="inlineStr">
         <is>
           <t>durationMs
 pondId</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="F52" s="2" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr">
+      <c r="G52" s="2" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>已实现</t>
-        </is>
-      </c>
-      <c r="I44" s="2" t="inlineStr">
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
         <is>
           <t>gameState.ts</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
         <is>
           <t>E性能</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
+      <c r="B53" s="2" t="inlineStr">
         <is>
           <t>socket_broadcast_fanout</t>
         </is>
       </c>
-      <c r="C45" s="2" t="inlineStr">
+      <c r="C53" s="2" t="inlineStr">
         <is>
           <t>指标+可选日志</t>
         </is>
       </c>
-      <c r="D45" s="2" t="inlineStr">
+      <c r="D53" s="2" t="inlineStr">
         <is>
           <t>广播 fanout；默认 Prometheus counter，FANOUT_LOG_INFO=1 才打 info</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="E53" s="2" t="inlineStr">
         <is>
           <t>fanoutCount
 channel
 pondId</t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr">
+      <c r="F53" s="2" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
-      <c r="G45" s="2" t="inlineStr">
+      <c r="G53" s="2" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="H45" s="2" t="inlineStr">
-        <is>
-          <t>已实现</t>
-        </is>
-      </c>
-      <c r="I45" s="2" t="inlineStr">
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
         <is>
           <t>serverLoops.ts</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>E性能</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
+      <c r="B54" s="2" t="inlineStr">
         <is>
           <t>sqlite_query_slow</t>
         </is>
       </c>
-      <c r="C46" s="2" t="inlineStr">
+      <c r="C54" s="2" t="inlineStr">
         <is>
           <t>日志</t>
         </is>
       </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="D54" s="2" t="inlineStr">
         <is>
           <t>慢 SQL</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="E54" s="2" t="inlineStr">
         <is>
           <t>label
 durationMs
 rows</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
+      <c r="F54" s="2" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr">
+      <c r="G54" s="2" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="H46" s="2" t="inlineStr">
-        <is>
-          <t>已实现</t>
-        </is>
-      </c>
-      <c r="I46" s="2" t="inlineStr">
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
         <is>
           <t>db.ts</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
         <is>
           <t>E性能</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
+      <c r="B55" s="2" t="inlineStr">
         <is>
           <t>admin_route_duration_ms</t>
         </is>
       </c>
-      <c r="C47" s="2" t="inlineStr">
+      <c r="C55" s="2" t="inlineStr">
         <is>
           <t>日志</t>
         </is>
       </c>
-      <c r="D47" s="2" t="inlineStr">
+      <c r="D55" s="2" t="inlineStr">
         <is>
           <t>Admin 接口耗时</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="E55" s="2" t="inlineStr">
         <is>
           <t>route
 durationMs</t>
         </is>
       </c>
-      <c r="F47" s="2" t="inlineStr">
+      <c r="F55" s="2" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
-      <c r="G47" s="2" t="inlineStr">
+      <c r="G55" s="2" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="H47" s="2" t="inlineStr">
-        <is>
-          <t>已实现</t>
-        </is>
-      </c>
-      <c r="I47" s="2" t="inlineStr">
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
         <is>
           <t>admin.ts</t>
         </is>
@@ -4442,7 +4827,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4772,7 +5157,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>{"speciesId":"crucian","sizeM":0.2,"gold":56,"sizeGainM":0.03}</t>
+          <t>{"speciesId":"crucian","sizeM":0.2,"gold":56,"sizeGainM":0.03,"auto":false}</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4788,6 +5173,247 @@
       <c r="I7" s="2" t="inlineStr">
         <is>
           <t>returnFish.ts</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>D成长进度</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>return_fee_mode_selected</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>metrics</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>进塘双价模式选择</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>playerId
+pondId</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>{"mode":"auto_return","feePer2h":350}</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>socketPondHandlers.ts</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>D成长进度</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>fish_auto_returned</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>metrics</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>达标鱼自动回塘</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>playerId
+pondId</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>{"speciesId":"crucian","sizeM":0.28,"gold":120,"auto":true}</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>returnFish.ts</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>D成长进度</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>achievement_unlocked</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>metrics</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>成就解锁</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>playerId
+achievementId</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>{"achievementId":"ach-first-catch"}</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>achievements.ts</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>D成长进度</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>album_pin_changed</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>metrics</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>相册钉选变更</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>playerId
+pinCount
+action</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>{"pinCount":3,"action":"pin"}</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>album.ts</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>D成长进度</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>profile_hub_opened</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>metrics</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>打开个人中心</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>playerId
+tab</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>{"tab":"album"}</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>profileHub.ts</t>
         </is>
       </c>
     </row>
@@ -4802,7 +5428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5053,6 +5679,150 @@
       <c r="I5" s="2" t="inlineStr">
         <is>
           <t>shop.ts</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>D装备</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>groundbait_cast_started</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>metrics</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>开始打窝扣金</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>playerId
+groundbaitId</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>{"costGold":30,"stackBefore":0}</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>groundbait.ts</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>D装备</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>groundbait_applied</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>metrics</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>打窝完成叠层</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>playerId
+pondId</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>{"stackAfter":1,"biteBonus":0.006}</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>groundbait.ts</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>D装备</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>groundbait_rejected</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>metrics</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>打窝拒绝</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>playerId
+reason</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>{"reason":"gold","code":"INSUFFICIENT_GOLD"}</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>groundbait.ts</t>
         </is>
       </c>
     </row>
